--- a/src/test/resources/testdata/LoginTestData.xlsx
+++ b/src/test/resources/testdata/LoginTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VineetArora2\Documents\learningfromscratch\com.ibm.NYCPortalTest\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2362BB9-F86E-4B0D-9F34-8B4A7D516706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD5DFF3-2074-4671-9D45-FAABF98D4F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>username</t>
   </si>
@@ -36,13 +36,16 @@
     <t>should_succeed</t>
   </si>
   <si>
-    <t>vineetarora2004@gmail.com</t>
-  </si>
-  <si>
-    <t>Vinaro#111</t>
-  </si>
-  <si>
     <t>vinasdad</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>test2@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -392,10 +395,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -403,10 +406,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
